--- a/excel/Max-Flow-Capacities-Full.xlsx
+++ b/excel/Max-Flow-Capacities-Full.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\home\boyko\opt2026\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6180820A-FF72-4E2F-97AB-7A427636949E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{051F4F38-4D55-4A63-9832-A22A15CF791C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4104" yWindow="3312" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4452" yWindow="3660" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="solver_adj" localSheetId="0" hidden="1">Sheet1!$B$7:$D$9</definedName>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">Sheet1!$B$13:$J$21</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="0" hidden="1">Sheet1!$B$10:$D$10</definedName>
-    <definedName name="solver_lhs2" localSheetId="0" hidden="1">Sheet1!$E$7:$E$9</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">Sheet1!$B$13:$J$21</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">Sheet1!$B$22:$I$22</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
@@ -32,13 +32,13 @@
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">Sheet1!$E$10</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">Sheet1!$J$22</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_rel1" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_rhs1" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_rhs2" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">Sheet1!$B$2:$J$10</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">Sheet1!$K$14:$K$21</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
@@ -504,10 +504,10 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -827,10 +827,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="1">
-        <v>5.3255212560063372</v>
+        <v>7</v>
       </c>
       <c r="C13" s="1">
-        <v>5.6744788953682397</v>
+        <v>4</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>6.999999998428355</v>
+        <v>12</v>
       </c>
       <c r="H13" s="1">
         <v>0</v>
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="1">
-        <v>5.3255212005481063</v>
+        <v>7</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="K14">
         <f>SUM(B14:J14)</f>
-        <v>5.3255212005481063</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -904,10 +904,10 @@
         <v>0</v>
       </c>
       <c r="D15" s="1">
-        <v>0.24170367490708664</v>
+        <v>4</v>
       </c>
       <c r="E15" s="1">
-        <v>5.4327751842421508</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -926,7 +926,7 @@
       </c>
       <c r="K15">
         <f t="shared" ref="K15:K21" si="0">SUM(B15:J15)</f>
-        <v>5.6744788591492377</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -955,14 +955,14 @@
         <v>0</v>
       </c>
       <c r="I16" s="1">
-        <v>5.5672248897723797</v>
+        <v>0</v>
       </c>
       <c r="J16" s="1">
         <v>0</v>
       </c>
       <c r="K16">
         <f t="shared" si="0"/>
-        <v>5.5672248897723797</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -982,7 +982,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>5.4327751900204344</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="K17">
         <f t="shared" si="0"/>
-        <v>5.4327751900204344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -1060,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="K19">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>7.4482984210111799E-9</v>
+        <v>0</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -1102,11 +1102,11 @@
         <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>7.000000140081533</v>
+        <v>12</v>
       </c>
       <c r="K20">
         <f t="shared" si="0"/>
-        <v>7.000000147529831</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>5.5672248897723788</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="K21">
         <f t="shared" si="0"/>
-        <v>5.5672248897723788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -1151,39 +1151,39 @@
       </c>
       <c r="B22">
         <f>SUM(B13:B21)</f>
-        <v>5.3255212560063372</v>
+        <v>7</v>
       </c>
       <c r="C22">
         <f t="shared" ref="C22:J22" si="1">SUM(C13:C21)</f>
-        <v>5.6744788953682397</v>
+        <v>4</v>
       </c>
       <c r="D22">
         <f t="shared" si="1"/>
-        <v>5.5672248754551932</v>
+        <v>11</v>
       </c>
       <c r="E22">
         <f t="shared" si="1"/>
-        <v>5.4327751916904488</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <f t="shared" si="1"/>
-        <v>11.000000079792812</v>
+        <v>11</v>
       </c>
       <c r="G22">
         <f t="shared" si="1"/>
-        <v>6.999999998428355</v>
+        <v>12</v>
       </c>
       <c r="H22">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I22">
         <f t="shared" si="1"/>
-        <v>5.5672248897723797</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2">
         <f t="shared" si="1"/>
-        <v>18.000000140081532</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
